--- a/data/trans_orig/P1415-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1415-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de problemas crónicos de la piel en 2012</t>
+          <t>Población con diagnóstico de problemas crónicos de la piel en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4386</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22722</t>
+          <t>21702</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8037</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24905</t>
+          <t>24436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414489</t>
+          <t>415509</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>432905</t>
+          <t>432825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>306417</t>
+          <t>306430</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313469</t>
+          <t>313467</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>726760</t>
+          <t>727229</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>744600</t>
+          <t>745184</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3295</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10762</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>23523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401171</t>
+          <t>401848</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415502</t>
+          <t>415628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327249</t>
+          <t>327604</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336145</t>
+          <t>336111</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>733806</t>
+          <t>733285</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>749875</t>
+          <t>749739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>20047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>9340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21898</t>
+          <t>23548</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>611016</t>
+          <t>609368</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>624522</t>
+          <t>624498</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251799</t>
+          <t>250789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259134</t>
+          <t>259139</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>867646</t>
+          <t>865996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>882604</t>
+          <t>882629</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12918</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31702</t>
+          <t>30727</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>13259</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16119</t>
+          <t>15919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37878</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1127307</t>
+          <t>1128282</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1146091</t>
+          <t>1147127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>750292</t>
+          <t>751463</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>762932</t>
+          <t>763071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885853</t>
+          <t>1885116</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907612</t>
+          <t>1907812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13232</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>17568</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9155</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24880</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>497364</t>
+          <t>498116</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508488</t>
+          <t>508490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>743594</t>
+          <t>742678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>755434</t>
+          <t>756135</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1245963</t>
+          <t>1245865</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1261688</t>
+          <t>1261624</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>863</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20566</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23943</t>
+          <t>23253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259151</t>
+          <t>259245</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266030</t>
+          <t>266019</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1088785</t>
+          <t>1089749</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1103267</t>
+          <t>1103279</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1352290</t>
+          <t>1352980</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1368166</t>
+          <t>1367879</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42962</t>
+          <t>42257</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75195</t>
+          <t>74802</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27282</t>
+          <t>25599</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51269</t>
+          <t>48913</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75958</t>
+          <t>74600</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>118205</t>
+          <t>115849</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3346715</t>
+          <t>3347108</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3378948</t>
+          <t>3379653</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3495646</t>
+          <t>3498002</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3519633</t>
+          <t>3521316</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6850620</t>
+          <t>6852976</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6892867</t>
+          <t>6894225</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de problemas crónicos de la piel en 2016</t>
+          <t>Población con diagnóstico de problemas crónicos de la piel en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>5019</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17237</t>
+          <t>17842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2864</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27481</t>
+          <t>27228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411855</t>
+          <t>411250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424356</t>
+          <t>424073</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>332572</t>
+          <t>333065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344117</t>
+          <t>344191</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>748666</t>
+          <t>748919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>766014</t>
+          <t>766523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>12133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12892</t>
+          <t>12056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18546</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365478</t>
+          <t>365094</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375318</t>
+          <t>375273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>359381</t>
+          <t>360217</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370161</t>
+          <t>370250</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>730954</t>
+          <t>731036</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744392</t>
+          <t>744092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>11173</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>977</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3478</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>15795</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510927</t>
+          <t>510741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520823</t>
+          <t>520976</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157712</t>
+          <t>157409</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165151</t>
+          <t>165146</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672336</t>
+          <t>672241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>684558</t>
+          <t>684993</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>6813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>21026</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32216</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1128422</t>
+          <t>1128612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1142534</t>
+          <t>1142825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>809181</t>
+          <t>809266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821100</t>
+          <t>821120</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1943298</t>
+          <t>1943773</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1961298</t>
+          <t>1962007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23036</t>
+          <t>21928</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25388</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>612857</t>
+          <t>612812</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>619873</t>
+          <t>619870</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715208</t>
+          <t>716316</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>730813</t>
+          <t>731299</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1333562</t>
+          <t>1334286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1349628</t>
+          <t>1349573</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3900</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28795</t>
+          <t>28978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30547</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>283245</t>
+          <t>282656</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1053230</t>
+          <t>1053047</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1071272</t>
+          <t>1071427</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1338623</t>
+          <t>1337832</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1357574</t>
+          <t>1357851</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>25069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48025</t>
+          <t>49511</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>42763</t>
+          <t>43184</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72180</t>
+          <t>73224</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74896</t>
+          <t>74238</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112280</t>
+          <t>111320</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3337697</t>
+          <t>3336211</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3361026</t>
+          <t>3360653</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3459416</t>
+          <t>3458372</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3488833</t>
+          <t>3488412</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6805038</t>
+          <t>6805998</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6842422</t>
+          <t>6843080</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1415-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1415-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21702</t>
+          <t>20523</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24436</t>
+          <t>24610</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415509</t>
+          <t>416688</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>432825</t>
+          <t>433010</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>306430</t>
+          <t>306293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>727229</t>
+          <t>727055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>745184</t>
+          <t>745475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23523</t>
+          <t>22574</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401848</t>
+          <t>401650</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>415628</t>
+          <t>415643</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327604</t>
+          <t>327838</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336111</t>
+          <t>336177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>733285</t>
+          <t>734234</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>749739</t>
+          <t>749949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4917</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20047</t>
+          <t>18708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609368</t>
+          <t>610707</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>624498</t>
+          <t>624440</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>250789</t>
+          <t>251779</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>259139</t>
+          <t>259137</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>865996</t>
+          <t>866471</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>882629</t>
+          <t>882501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30727</t>
+          <t>32933</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1647</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>39020</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1128282</t>
+          <t>1126076</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1147127</t>
+          <t>1146198</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>751463</t>
+          <t>751102</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>763071</t>
+          <t>763075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885116</t>
+          <t>1884711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1907812</t>
+          <t>1907449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17568</t>
+          <t>17573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24978</t>
+          <t>24077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>498116</t>
+          <t>497463</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>508490</t>
+          <t>508491</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742678</t>
+          <t>742673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>756135</t>
+          <t>756121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1245865</t>
+          <t>1246766</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1261624</t>
+          <t>1261792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>867</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19602</t>
+          <t>19645</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8354</t>
+          <t>8074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23253</t>
+          <t>24637</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259245</t>
+          <t>258664</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>266019</t>
+          <t>266015</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1089749</t>
+          <t>1089706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1103279</t>
+          <t>1103179</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1352980</t>
+          <t>1351596</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1367879</t>
+          <t>1368159</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42257</t>
+          <t>43261</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74802</t>
+          <t>75204</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25599</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48913</t>
+          <t>52458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74600</t>
+          <t>74230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115849</t>
+          <t>114140</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3347108</t>
+          <t>3346706</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3379653</t>
+          <t>3378649</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3498002</t>
+          <t>3494457</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3521316</t>
+          <t>3521555</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6852976</t>
+          <t>6854685</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6894225</t>
+          <t>6894595</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5019</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>10062</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>27228</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>411250</t>
+          <t>411387</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424073</t>
+          <t>424596</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>333065</t>
+          <t>332783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>344191</t>
+          <t>344028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>748919</t>
+          <t>749826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>766523</t>
+          <t>766085</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>11579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365094</t>
+          <t>365648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>375273</t>
+          <t>375328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360217</t>
+          <t>360728</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370250</t>
+          <t>370280</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731036</t>
+          <t>730421</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744092</t>
+          <t>744138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>1079</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>8490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>510741</t>
+          <t>511043</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520976</t>
+          <t>520835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>157409</t>
+          <t>157633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165146</t>
+          <t>165151</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>672241</t>
+          <t>671654</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>684993</t>
+          <t>684466</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>20816</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13507</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1128612</t>
+          <t>1128822</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1142825</t>
+          <t>1142854</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>809266</t>
+          <t>808972</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>821120</t>
+          <t>821041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1943773</t>
+          <t>1943688</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1962007</t>
+          <t>1961506</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21928</t>
+          <t>21989</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9377</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24664</t>
+          <t>26148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>612812</t>
+          <t>613272</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4886,12 +4886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>716316</t>
+          <t>716255</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>731299</t>
+          <t>730852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4901,12 +4901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4921,12 +4921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1334286</t>
+          <t>1332802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1349573</t>
+          <t>1348827</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4936,12 +4936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10598</t>
+          <t>9977</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28978</t>
+          <t>29429</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31338</t>
+          <t>30010</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282656</t>
+          <t>282133</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1053047</t>
+          <t>1052596</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1071427</t>
+          <t>1072048</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1337832</t>
+          <t>1339160</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1357851</t>
+          <t>1357933</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -5424,12 +5424,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25069</t>
+          <t>25447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49511</t>
+          <t>48287</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43184</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>73224</t>
+          <t>74392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74238</t>
+          <t>73025</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111320</t>
+          <t>113039</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5509,12 +5509,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -5537,12 +5537,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3336211</t>
+          <t>3337435</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3360653</t>
+          <t>3360275</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5572,12 +5572,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3458372</t>
+          <t>3457204</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3488412</t>
+          <t>3488401</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6805998</t>
+          <t>6804279</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6843080</t>
+          <t>6844293</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
